--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEVADA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEVADA_2015.xlsx
@@ -517,7 +517,7 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="10">
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="22">
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="D25">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="26">
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="D26">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="27">
@@ -1111,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="D42">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="43">
@@ -1129,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="D43">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="44">
@@ -1255,7 +1255,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="51">
@@ -1273,7 +1273,7 @@
         <v>2</v>
       </c>
       <c r="D51">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="52">
@@ -1399,7 +1399,7 @@
         <v>2</v>
       </c>
       <c r="D58">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="59">
@@ -1489,7 +1489,7 @@
         <v>2</v>
       </c>
       <c r="D63">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="64">
@@ -1507,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="D64">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="65">
@@ -1633,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="D71">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="72">
@@ -1705,7 +1705,7 @@
         <v>2</v>
       </c>
       <c r="D75">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="76">
@@ -1777,7 +1777,7 @@
         <v>2</v>
       </c>
       <c r="D79">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="80">
@@ -1867,7 +1867,7 @@
         <v>2</v>
       </c>
       <c r="D84">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="85">
@@ -2101,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="D97">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="98">
@@ -2137,7 +2137,7 @@
         <v>2</v>
       </c>
       <c r="D99">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="100">
@@ -2299,7 +2299,7 @@
         <v>2</v>
       </c>
       <c r="D108">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="109">
@@ -2461,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="D117">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="118">
@@ -2515,7 +2515,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="121">
@@ -2551,7 +2551,7 @@
         <v>2</v>
       </c>
       <c r="D122">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="123">
@@ -2569,7 +2569,7 @@
         <v>2</v>
       </c>
       <c r="D123">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="124">
@@ -2587,7 +2587,7 @@
         <v>2</v>
       </c>
       <c r="D124">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="125">
@@ -2767,7 +2767,7 @@
         <v>2</v>
       </c>
       <c r="D134">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="135">
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="D138">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="139">
@@ -2929,7 +2929,7 @@
         <v>2</v>
       </c>
       <c r="D143">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="144">
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
       <c r="D145">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="146">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C180">
@@ -3721,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="D187">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="188">
@@ -3793,7 +3793,7 @@
         <v>19</v>
       </c>
       <c r="D191">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="192">
@@ -3829,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="D193">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="194">
@@ -4009,7 +4009,7 @@
         <v>2</v>
       </c>
       <c r="D203">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="204">
@@ -4153,7 +4153,7 @@
         <v>2</v>
       </c>
       <c r="D211">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="212">
@@ -4171,7 +4171,7 @@
         <v>2</v>
       </c>
       <c r="D212">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="213">
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="D213">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="214">
@@ -4675,7 +4675,7 @@
         <v>2</v>
       </c>
       <c r="D240">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="241">
@@ -4729,7 +4729,7 @@
         <v>2</v>
       </c>
       <c r="D243">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="244">
@@ -4783,7 +4783,7 @@
         <v>2</v>
       </c>
       <c r="D246">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="247">
@@ -4927,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="D254">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="255">
@@ -4999,7 +4999,7 @@
         <v>2</v>
       </c>
       <c r="D258">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="259">
@@ -5431,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="D282">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="283">
@@ -5503,7 +5503,7 @@
         <v>2</v>
       </c>
       <c r="D286">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="287">
@@ -5575,7 +5575,7 @@
         <v>2</v>
       </c>
       <c r="D290">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="291">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C308">
@@ -6475,7 +6475,7 @@
         <v>2</v>
       </c>
       <c r="D340">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="341">
@@ -7087,7 +7087,7 @@
         <v>2</v>
       </c>
       <c r="D374">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="375">
@@ -7393,7 +7393,7 @@
         <v>20</v>
       </c>
       <c r="D391">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="392">
@@ -7591,7 +7591,7 @@
         <v>2</v>
       </c>
       <c r="D402">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="403">
@@ -7681,7 +7681,7 @@
         <v>2</v>
       </c>
       <c r="D407">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="408">
@@ -7717,7 +7717,7 @@
         <v>2</v>
       </c>
       <c r="D409">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="410">
@@ -7735,7 +7735,7 @@
         <v>2</v>
       </c>
       <c r="D410">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="411">
@@ -7897,7 +7897,7 @@
         <v>2</v>
       </c>
       <c r="D419">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="420">
@@ -8077,7 +8077,7 @@
         <v>2</v>
       </c>
       <c r="D429">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="430">
@@ -8167,7 +8167,7 @@
         <v>2</v>
       </c>
       <c r="D434">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="435">
@@ -8203,7 +8203,7 @@
         <v>2</v>
       </c>
       <c r="D436">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="437">
@@ -8347,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="D444">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="445">
@@ -8491,7 +8491,7 @@
         <v>2</v>
       </c>
       <c r="D452">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="453">
@@ -8797,7 +8797,7 @@
         <v>2</v>
       </c>
       <c r="D469">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="470">
@@ -9301,7 +9301,7 @@
         <v>20</v>
       </c>
       <c r="D497">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="498">
@@ -9319,7 +9319,7 @@
         <v>19</v>
       </c>
       <c r="D498">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="499">
@@ -9391,7 +9391,7 @@
         <v>2</v>
       </c>
       <c r="D502">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="503">
@@ -9445,7 +9445,7 @@
         <v>2</v>
       </c>
       <c r="D505">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="506">
@@ -9805,7 +9805,7 @@
         <v>2</v>
       </c>
       <c r="D525">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="526">
@@ -10039,7 +10039,7 @@
         <v>2</v>
       </c>
       <c r="D538">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="539">
@@ -10057,7 +10057,7 @@
         <v>20</v>
       </c>
       <c r="D539">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="540">
@@ -10129,7 +10129,7 @@
         <v>2</v>
       </c>
       <c r="D543">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="544">
@@ -10507,7 +10507,7 @@
         <v>2</v>
       </c>
       <c r="D564">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="565">
@@ -10579,7 +10579,7 @@
         <v>19</v>
       </c>
       <c r="D568">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="569">
@@ -11263,7 +11263,7 @@
         <v>2</v>
       </c>
       <c r="D606">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="607">
@@ -11533,7 +11533,7 @@
         <v>19</v>
       </c>
       <c r="D621">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="622">
@@ -11893,7 +11893,7 @@
         <v>2</v>
       </c>
       <c r="D641">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="642">
@@ -12487,7 +12487,7 @@
         <v>2</v>
       </c>
       <c r="D674">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="675">
@@ -12523,7 +12523,7 @@
         <v>2</v>
       </c>
       <c r="D676">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="677">
@@ -12865,7 +12865,7 @@
         <v>2</v>
       </c>
       <c r="D695">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="696">
@@ -13351,7 +13351,7 @@
         <v>2</v>
       </c>
       <c r="D722">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="723">
@@ -13405,7 +13405,7 @@
         <v>2</v>
       </c>
       <c r="D725">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="726">
@@ -13477,7 +13477,7 @@
         <v>2</v>
       </c>
       <c r="D729">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="730">
@@ -13531,7 +13531,7 @@
         <v>2</v>
       </c>
       <c r="D732">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="733">
@@ -13603,7 +13603,7 @@
         <v>2</v>
       </c>
       <c r="D736">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="737">
@@ -13765,7 +13765,7 @@
         <v>2</v>
       </c>
       <c r="D745">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="746">
@@ -14179,7 +14179,7 @@
         <v>2</v>
       </c>
       <c r="D768">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="769">
@@ -14575,7 +14575,7 @@
         <v>2</v>
       </c>
       <c r="D790">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="791">
@@ -14665,7 +14665,7 @@
         <v>2</v>
       </c>
       <c r="D795">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="796">
@@ -14737,7 +14737,7 @@
         <v>2</v>
       </c>
       <c r="D799">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="800">
@@ -14845,7 +14845,7 @@
         <v>2</v>
       </c>
       <c r="D805">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="806">
@@ -14881,7 +14881,7 @@
         <v>2</v>
       </c>
       <c r="D807">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="808">
@@ -15043,7 +15043,7 @@
         <v>2</v>
       </c>
       <c r="D816">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="817">
@@ -15187,7 +15187,7 @@
         <v>2</v>
       </c>
       <c r="D824">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="825">
@@ -15547,7 +15547,7 @@
         <v>2</v>
       </c>
       <c r="D844">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="845">
@@ -15558,14 +15558,14 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C845">
         <v>2</v>
       </c>
       <c r="D845">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="846">
@@ -15727,7 +15727,7 @@
         <v>2</v>
       </c>
       <c r="D854">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="855">
@@ -15925,7 +15925,7 @@
         <v>2</v>
       </c>
       <c r="D865">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="866">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C870">
@@ -16051,7 +16051,7 @@
         <v>2</v>
       </c>
       <c r="D872">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="873">
@@ -16069,7 +16069,7 @@
         <v>2</v>
       </c>
       <c r="D873">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="874">
@@ -16231,7 +16231,7 @@
         <v>2</v>
       </c>
       <c r="D882">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="883">
@@ -16267,7 +16267,7 @@
         <v>2</v>
       </c>
       <c r="D884">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="885">
@@ -16321,7 +16321,7 @@
         <v>2</v>
       </c>
       <c r="D887">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="888">
@@ -16537,7 +16537,7 @@
         <v>2</v>
       </c>
       <c r="D899">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="900">
@@ -16591,7 +16591,7 @@
         <v>2</v>
       </c>
       <c r="D902">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="903">
@@ -16627,7 +16627,7 @@
         <v>2</v>
       </c>
       <c r="D904">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="905">
@@ -16645,7 +16645,7 @@
         <v>2</v>
       </c>
       <c r="D905">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="906">
@@ -16735,7 +16735,7 @@
         <v>2</v>
       </c>
       <c r="D910">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="911">
@@ -16861,7 +16861,7 @@
         <v>2</v>
       </c>
       <c r="D917">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="918">
@@ -16897,7 +16897,7 @@
         <v>2</v>
       </c>
       <c r="D919">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="920">
@@ -16987,7 +16987,7 @@
         <v>2</v>
       </c>
       <c r="D924">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="925">
@@ -17005,7 +17005,7 @@
         <v>2</v>
       </c>
       <c r="D925">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="926">
@@ -17041,7 +17041,7 @@
         <v>2</v>
       </c>
       <c r="D927">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="928">
@@ -17077,7 +17077,7 @@
         <v>2</v>
       </c>
       <c r="D929">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="930">
@@ -17095,7 +17095,7 @@
         <v>2</v>
       </c>
       <c r="D930">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="931">
@@ -17149,7 +17149,7 @@
         <v>2</v>
       </c>
       <c r="D933">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="934">
@@ -17167,7 +17167,7 @@
         <v>2</v>
       </c>
       <c r="D934">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="935">
@@ -17401,7 +17401,7 @@
         <v>2</v>
       </c>
       <c r="D947">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="948">
@@ -17473,7 +17473,7 @@
         <v>2</v>
       </c>
       <c r="D951">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="952">
@@ -17491,7 +17491,7 @@
         <v>19</v>
       </c>
       <c r="D952">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="953">
@@ -17581,7 +17581,7 @@
         <v>2</v>
       </c>
       <c r="D957">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="958">
@@ -17707,7 +17707,7 @@
         <v>2</v>
       </c>
       <c r="D964">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="965">
@@ -17725,7 +17725,7 @@
         <v>2</v>
       </c>
       <c r="D965">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="966">
@@ -17833,7 +17833,7 @@
         <v>2</v>
       </c>
       <c r="D971">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="972">
@@ -17869,7 +17869,7 @@
         <v>2</v>
       </c>
       <c r="D973">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="974">
@@ -18031,7 +18031,7 @@
         <v>2</v>
       </c>
       <c r="D982">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="983">
@@ -18049,7 +18049,7 @@
         <v>2</v>
       </c>
       <c r="D983">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="984">
@@ -18193,7 +18193,7 @@
         <v>2</v>
       </c>
       <c r="D991">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="992">
@@ -18247,7 +18247,7 @@
         <v>2</v>
       </c>
       <c r="D994">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="995">
@@ -18373,7 +18373,7 @@
         <v>2</v>
       </c>
       <c r="D1001">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1002">
@@ -18463,7 +18463,7 @@
         <v>2</v>
       </c>
       <c r="D1006">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1007">
@@ -18625,7 +18625,7 @@
         <v>2</v>
       </c>
       <c r="D1015">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1016">
@@ -18751,7 +18751,7 @@
         <v>2</v>
       </c>
       <c r="D1022">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1023">
@@ -18895,7 +18895,7 @@
         <v>2</v>
       </c>
       <c r="D1030">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1031">
@@ -19093,7 +19093,7 @@
         <v>2</v>
       </c>
       <c r="D1041">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1042">
@@ -19129,7 +19129,7 @@
         <v>19</v>
       </c>
       <c r="D1043">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="1044">
@@ -19219,7 +19219,7 @@
         <v>20</v>
       </c>
       <c r="D1048">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="1049">
@@ -19327,7 +19327,7 @@
         <v>2</v>
       </c>
       <c r="D1054">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19471,7 +19471,7 @@
         <v>2</v>
       </c>
       <c r="D1062">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1063">
@@ -19561,7 +19561,7 @@
         <v>2</v>
       </c>
       <c r="D1067">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1068">
@@ -19615,7 +19615,7 @@
         <v>2</v>
       </c>
       <c r="D1070">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1071">
@@ -19633,7 +19633,7 @@
         <v>2</v>
       </c>
       <c r="D1071">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1072">
@@ -19777,7 +19777,7 @@
         <v>2</v>
       </c>
       <c r="D1079">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1080">
@@ -19939,7 +19939,7 @@
         <v>2</v>
       </c>
       <c r="D1088">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1089">
@@ -19993,7 +19993,7 @@
         <v>2</v>
       </c>
       <c r="D1091">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1092">
@@ -20101,7 +20101,7 @@
         <v>2</v>
       </c>
       <c r="D1097">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1098">
@@ -20371,7 +20371,7 @@
         <v>2</v>
       </c>
       <c r="D1112">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1113">
@@ -20425,7 +20425,7 @@
         <v>2</v>
       </c>
       <c r="D1115">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1116">
@@ -20695,7 +20695,7 @@
         <v>2</v>
       </c>
       <c r="D1130">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1131">
@@ -20713,7 +20713,7 @@
         <v>2</v>
       </c>
       <c r="D1131">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1132">
@@ -20965,7 +20965,7 @@
         <v>2</v>
       </c>
       <c r="D1145">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1146">
@@ -20983,7 +20983,7 @@
         <v>2</v>
       </c>
       <c r="D1146">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1147">
@@ -21073,7 +21073,7 @@
         <v>2</v>
       </c>
       <c r="D1151">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1152">
@@ -21271,7 +21271,7 @@
         <v>19</v>
       </c>
       <c r="D1162">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="1163">
@@ -21343,7 +21343,7 @@
         <v>20</v>
       </c>
       <c r="D1166">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="1167">
@@ -21433,7 +21433,7 @@
         <v>2</v>
       </c>
       <c r="D1171">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1172">
@@ -21541,7 +21541,7 @@
         <v>19</v>
       </c>
       <c r="D1177">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="1178">
@@ -21685,7 +21685,7 @@
         <v>2</v>
       </c>
       <c r="D1185">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1186">
@@ -21847,7 +21847,7 @@
         <v>2</v>
       </c>
       <c r="D1194">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1195">
@@ -21883,7 +21883,7 @@
         <v>2</v>
       </c>
       <c r="D1196">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1197">
@@ -21919,7 +21919,7 @@
         <v>2</v>
       </c>
       <c r="D1198">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1199">
@@ -22117,7 +22117,7 @@
         <v>2</v>
       </c>
       <c r="D1209">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1210">
@@ -22153,7 +22153,7 @@
         <v>2</v>
       </c>
       <c r="D1211">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1212">
@@ -22171,7 +22171,7 @@
         <v>2</v>
       </c>
       <c r="D1212">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1213">
@@ -22225,7 +22225,7 @@
         <v>2</v>
       </c>
       <c r="D1215">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1216">
@@ -22315,7 +22315,7 @@
         <v>2</v>
       </c>
       <c r="D1220">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1221">
@@ -22369,7 +22369,7 @@
         <v>2</v>
       </c>
       <c r="D1223">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1224">
@@ -22441,7 +22441,7 @@
         <v>2</v>
       </c>
       <c r="D1227">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1228">
@@ -22639,7 +22639,7 @@
         <v>2</v>
       </c>
       <c r="D1238">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1239">
@@ -22765,7 +22765,7 @@
         <v>2</v>
       </c>
       <c r="D1245">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1246">
@@ -22783,7 +22783,7 @@
         <v>2</v>
       </c>
       <c r="D1246">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1247">
@@ -22819,7 +22819,7 @@
         <v>2</v>
       </c>
       <c r="D1248">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1249">
@@ -22855,7 +22855,7 @@
         <v>2</v>
       </c>
       <c r="D1250">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1251">
@@ -23089,7 +23089,7 @@
         <v>2</v>
       </c>
       <c r="D1263">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1264">
@@ -23107,7 +23107,7 @@
         <v>2</v>
       </c>
       <c r="D1264">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1265">
@@ -23125,7 +23125,7 @@
         <v>2</v>
       </c>
       <c r="D1265">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1266">
@@ -23215,7 +23215,7 @@
         <v>2</v>
       </c>
       <c r="D1270">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1271">
@@ -23341,7 +23341,7 @@
         <v>2</v>
       </c>
       <c r="D1277">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1278">
@@ -23395,7 +23395,7 @@
         <v>2</v>
       </c>
       <c r="D1280">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1281">
@@ -23575,7 +23575,7 @@
         <v>2</v>
       </c>
       <c r="D1290">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1291">
@@ -23683,7 +23683,7 @@
         <v>2</v>
       </c>
       <c r="D1296">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1297">
@@ -23809,7 +23809,7 @@
         <v>2</v>
       </c>
       <c r="D1303">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1304">
@@ -23917,7 +23917,7 @@
         <v>2</v>
       </c>
       <c r="D1309">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1310">
@@ -23989,7 +23989,7 @@
         <v>2</v>
       </c>
       <c r="D1313">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1314">
@@ -24007,7 +24007,7 @@
         <v>2</v>
       </c>
       <c r="D1314">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1315">
@@ -24061,7 +24061,7 @@
         <v>2</v>
       </c>
       <c r="D1317">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1318">
@@ -24277,7 +24277,7 @@
         <v>20</v>
       </c>
       <c r="D1329">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="1330">
@@ -24349,7 +24349,7 @@
         <v>2</v>
       </c>
       <c r="D1333">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1334">
@@ -24385,7 +24385,7 @@
         <v>2</v>
       </c>
       <c r="D1335">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1336">
@@ -24439,7 +24439,7 @@
         <v>2</v>
       </c>
       <c r="D1338">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1339">
@@ -24565,7 +24565,7 @@
         <v>2</v>
       </c>
       <c r="D1345">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1346">
@@ -24583,7 +24583,7 @@
         <v>2</v>
       </c>
       <c r="D1346">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1347">
@@ -24691,7 +24691,7 @@
         <v>2</v>
       </c>
       <c r="D1352">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1353">
@@ -24763,7 +24763,7 @@
         <v>2</v>
       </c>
       <c r="D1356">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1357">
@@ -24781,7 +24781,7 @@
         <v>2</v>
       </c>
       <c r="D1357">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1358">
@@ -24979,7 +24979,7 @@
         <v>2</v>
       </c>
       <c r="D1368">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1369">
@@ -25069,7 +25069,7 @@
         <v>2</v>
       </c>
       <c r="D1373">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1374">
@@ -25195,7 +25195,7 @@
         <v>2</v>
       </c>
       <c r="D1380">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1381">
@@ -25303,7 +25303,7 @@
         <v>2</v>
       </c>
       <c r="D1386">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1387">
@@ -25321,7 +25321,7 @@
         <v>2</v>
       </c>
       <c r="D1387">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1388">
@@ -25357,7 +25357,7 @@
         <v>20</v>
       </c>
       <c r="D1389">
-        <v>0.0009888262632255513</v>
+        <v>0.0009888262632255511</v>
       </c>
     </row>
     <row r="1390">
@@ -25429,7 +25429,7 @@
         <v>2</v>
       </c>
       <c r="D1393">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1394">
@@ -25681,7 +25681,7 @@
         <v>2</v>
       </c>
       <c r="D1407">
-        <v>9.888262632255513E-05</v>
+        <v>9.888262632255512E-05</v>
       </c>
     </row>
     <row r="1408">
@@ -25843,7 +25843,7 @@
         <v>19</v>
       </c>
       <c r="D1416">
-        <v>0.0009393849500642737</v>
+        <v>0.0009393849500642736</v>
       </c>
     </row>
     <row r="1417">
